--- a/api/tests/forecast/fixtures/forecast_model_synthetic_complete.xlsx
+++ b/api/tests/forecast/fixtures/forecast_model_synthetic_complete.xlsx
@@ -1748,7 +1748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AE8"/>
+  <dimension ref="A2:AE10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -2155,6 +2155,169 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>Person G3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>VMS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Staffing</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>90</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>168</v>
+      </c>
+      <c r="M8" t="n">
+        <v>160</v>
+      </c>
+      <c r="O8" t="n">
+        <v>15120</v>
+      </c>
+      <c r="P8" t="n">
+        <v>14400</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>160</v>
+      </c>
+      <c r="R8" t="n">
+        <v>152</v>
+      </c>
+      <c r="T8" t="n">
+        <v>14400</v>
+      </c>
+      <c r="U8" t="n">
+        <v>13680</v>
+      </c>
+      <c r="V8" t="n">
+        <v>176</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>15840</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>176</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Person G4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Analyst</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>VMS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Staffing</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>90</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>168</v>
+      </c>
+      <c r="M9" t="n">
+        <v>160</v>
+      </c>
+      <c r="O9" t="n">
+        <v>15120</v>
+      </c>
+      <c r="P9" t="n">
+        <v>14400</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>160</v>
+      </c>
+      <c r="R9" t="n">
+        <v>152</v>
+      </c>
+      <c r="T9" t="n">
+        <v>14400</v>
+      </c>
+      <c r="U9" t="n">
+        <v>13680</v>
+      </c>
+      <c r="V9" t="n">
+        <v>176</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>15840</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>176</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>15840</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
